--- a/assets/data/excel/chips.xlsx
+++ b/assets/data/excel/chips.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="强化芯片表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chips" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>英文名</t>
+          <t>英文名称</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>生命百分比</t>
+          <t>生命百分比加成</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>攻击百分比</t>
+          <t>攻击百分比加成</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -590,17 +590,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHIP_N001</t>
+          <t>CHIP_N_ATK_01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>铁皮芯片</t>
+          <t>锈蚀增幅芯片</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iron Skin Chip</t>
+          <t>Rust Amplifier Chip</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -631,29 +631,29 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CSK001</t>
+          <t>["CSK001"]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>基础防御芯片，略微提升生命值</t>
+          <t>基础攻击芯片，锈蚀电路微量提升攻击力3%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHIP_N002</t>
+          <t>CHIP_N_DEF_01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>利刃芯片</t>
+          <t>废铁壁垒芯片</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sharp Blade Chip</t>
+          <t>Scrap Barricade Chip</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -662,14 +662,14 @@
         </is>
       </c>
       <c r="E5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>all</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -684,29 +684,29 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CSK002</t>
+          <t>["CSK012"]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>基础攻击芯片，略微提升攻击力</t>
+          <t>基础防御芯片，废铁焊接提升生命值5%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHIP_N003</t>
+          <t>CHIP_N_FNC_01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>速动芯片</t>
+          <t>废料回收芯片</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Quick Action Chip</t>
+          <t>Scrap Recycler Chip</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -737,29 +737,29 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CSK003</t>
+          <t>["CSK022"]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>基础均衡芯片，微量提升攻防</t>
+          <t>基础功能芯片，内置回收模块每回合恢复3%生命</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHIP_R001</t>
+          <t>CHIP_R_ATK_01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>守护之心</t>
+          <t>过载脉冲芯片</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Guardian Heart</t>
+          <t>Overload Pulse Chip</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -768,14 +768,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tank,support</t>
+          <t>all</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -790,29 +790,29 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CSK004,CSK005</t>
+          <t>["CSK002"]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>防御型芯片，显著提升生命值，附带减伤光环</t>
+          <t>改良攻击芯片，过载脉冲攻击时附带8%真实伤害</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHIP_R002</t>
+          <t>CHIP_R_DEF_01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>猎手之眼</t>
+          <t>辐射硬化芯片</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hunter's Eye</t>
+          <t>Radiation Hardening Chip</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -821,14 +821,14 @@
         </is>
       </c>
       <c r="E8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
-        <v>8</v>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>damage,assassin</t>
+          <t>all</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -843,29 +843,29 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CSK006</t>
+          <t>["CSK013"]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>攻击型芯片，提升暴击率和攻击力</t>
+          <t>改良防御芯片，辐射硬化受击时获得5%最大生命护盾</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHIP_R003</t>
+          <t>CHIP_R_FNC_01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>元素导体</t>
+          <t>肾上腺素泵芯片</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Elemental Conduit</t>
+          <t>Adrenaline Pump Chip</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>fire,ice,thunder</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -896,29 +896,29 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>CSK007</t>
+          <t>["CSK023"]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>元素型芯片，提升元素伤害输出</t>
+          <t>改良功能芯片，内置肾上腺素泵战斗开始提速10%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHIP_SR001</t>
+          <t>CHIP_SR_ATK_01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>不灭壁垒</t>
+          <t>热能导引芯片</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Immortal Bastion</t>
+          <t>Thermal Guidance Chip</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -927,14 +927,14 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>dps</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -944,34 +944,34 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>mech,plant</t>
+          <t>all</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>CSK008,CSK009</t>
+          <t>["CSK003"]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>高级防御芯片，大幅提升生命值，受击时有概率获得护盾</t>
+          <t>精密攻击芯片，限定输出职业，永久提升暴击率5%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHIP_SR002</t>
+          <t>CHIP_SR_DEF_01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>致命打击</t>
+          <t>合金镀层芯片</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lethal Strike</t>
+          <t>Alloy Coating Chip</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -980,14 +980,14 @@
         </is>
       </c>
       <c r="E11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="n">
-        <v>12</v>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>damage,berserker</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -997,34 +997,34 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>animal,energy</t>
+          <t>all</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CSK010,CSK011</t>
+          <t>["CSK014"]</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>高级攻击芯片，大幅提升攻击力，暴击时附加额外伤害</t>
+          <t>精密防御芯片，限定坦克职业，减伤率提升5%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHIP_SR003</t>
+          <t>CHIP_SR_FNC_01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>战术核心</t>
+          <t>扫描模块芯片</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tactical Core</t>
+          <t>Scan Module Chip</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1055,29 +1055,29 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>CSK012,CSK013</t>
+          <t>["CSK024"]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>高级均衡芯片，全面提升属性，附带战术分析效果</t>
+          <t>精密功能芯片，战术扫描模块提升暴击率3%和闪避率3%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHIP_SSR001</t>
+          <t>CHIP_SSR_ATK_01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>方舟之盾</t>
+          <t>裂变弹头芯片</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ark Shield</t>
+          <t>Fission Warhead Chip</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1086,19 +1086,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>0.05</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>0.15</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tank,support</t>
+          <t>dps</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1108,29 +1108,29 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CSK014,CSK015,CSK016</t>
+          <t>["CSK004", "CSK005"]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>传说防御芯片，极大提升生命值，光属性角色额外获得圣光庇护</t>
+          <t>高级攻击芯片，限定火系输出，攻击力提升8%并附带12%真实伤害</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHIP_SSR002</t>
+          <t>CHIP_SSR_DEF_01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>深渊之刃</t>
+          <t>纳米修复芯片</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Abyss Blade</t>
+          <t>Nano Repair Chip</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>damage,assassin,berserker</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>water</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1161,29 +1161,29 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>CSK017,CSK018,CSK019</t>
+          <t>["CSK015", "CSK016"]</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>传说攻击芯片，极大提升攻击力，暗属性角色暴击伤害额外提升</t>
+          <t>高级防御芯片，限定水系坦克，生命值提升10%并每回合恢复6%生命</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHIP_SSR003</t>
+          <t>CHIP_SSR_FNC_01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>混沌之心</t>
+          <t>电磁加速芯片</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chaos Heart</t>
+          <t>EM Accelerator Chip</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>0.05</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1204,39 +1204,39 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>all</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>CSK020,CSK021</t>
+          <t>["CSK025", "CSK026"]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>传说均衡芯片，混合系专属，全面提升并触发混沌共鸣</t>
+          <t>高级功能芯片，限定风系，战斗开始攻击力与速度提升8%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHIP_UR001</t>
+          <t>CHIP_UR_ATK_01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>永恒堡垒</t>
+          <t>反物质裂解芯片</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eternal Fortress</t>
+          <t>Antimatter Fission Chip</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>0.1</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>0.22</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>dps</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1267,29 +1267,29 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>CSK022,CSK023,CSK024</t>
+          <t>["CSK007", "CSK008"]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>史诗防御芯片，极限生命提升，战斗开始时获得巨额护盾</t>
+          <t>超稀有攻击芯片，限定暗系输出，攻击力提升15%并附带18%真实伤害</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHIP_UR002</t>
+          <t>CHIP_UR_DEF_01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>末日审判</t>
+          <t>超导磁力场芯片</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Doom Judgment</t>
+          <t>Superconductor Field Chip</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1298,19 +1298,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>0.28</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>damage,berserker</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>light</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1320,29 +1320,29 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CSK025,CSK026,CSK027</t>
+          <t>["CSK017", "CSK018"]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>史诗攻击芯片，极限攻击提升，攻击附带无视防御的真实伤害</t>
+          <t>超稀有防御芯片，限定光系坦克，受击获得10%护盾，减伤率提升12%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHIP_UR003</t>
+          <t>CHIP_UR_FNC_01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>万象归一</t>
+          <t>全息诱饵芯片</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Universal Unity</t>
+          <t>Holographic Decoy Chip</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1351,14 +1351,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>0.05</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>0.08</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>support</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1373,29 +1373,29 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CSK028,CSK029,CSK030</t>
+          <t>["CSK027", "CSK028"]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>史诗万能芯片，全属性大幅提升，每回合随机触发一种强化效果</t>
+          <t>超稀有功能芯片，限定辅助职业，每回合恢复8%生命，受击闪避率提升15%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHIP_LE001</t>
+          <t>CHIP_LE_ATK_01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>创世神盾</t>
+          <t>量子隧穿芯片</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Genesis Aegis</t>
+          <t>Quantum Tunneling Chip</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1404,14 +1404,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>0.15</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>0.35</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tank,support</t>
+          <t>dps</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1421,34 +1421,34 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>mech</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>CSK031,CSK032,CSK033,CSK034</t>
+          <t>["CSK009", "CSK010", "CSK011"]</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>神话防御芯片，生命值极限提升，濒死时自动触发无敌保护</t>
+          <t>传说攻击芯片，限定机械系输出，无视防御25%真实伤害，击杀时全体30%真实伤害</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHIP_LE002</t>
+          <t>CHIP_LE_DEF_01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>湮灭之矛</t>
+          <t>维度折叠壁垒芯片</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Annihilation Spear</t>
+          <t>Dimensional Fold Barrier Chip</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1457,14 +1457,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>0.45</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>damage,assassin,berserker</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1474,34 +1474,34 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CSK035,CSK036,CSK037,CSK038</t>
+          <t>["CSK019", "CSK020", "CSK021"]</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>神话攻击芯片，攻击力极限提升，击杀敌人后连续行动一次</t>
+          <t>传说防御芯片，限定能量系坦克，生命值提升20%，减伤15%，危急时25%护盾</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHIP_LE003</t>
+          <t>CHIP_LE_FNC_01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>世界树之种</t>
+          <t>奇点引擎芯片</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>World Tree Seed</t>
+          <t>Singularity Engine Chip</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1510,14 +1510,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>30</v>
+        <v>0.2</v>
       </c>
       <c r="F21" t="n">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>support</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1527,17 +1527,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CSK039,CSK040,CSK041,CSK042</t>
+          <t>["CSK029", "CSK030", "CSK031"]</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>神话万能芯片，全属性极限提升，每回合为全体友军提供持续增益</t>
+          <t>传说功能芯片，限定混合系辅助，全体增益10%攻速，危急时额外行动+20%攻击</t>
         </is>
       </c>
     </row>

--- a/assets/data/excel/chips.xlsx
+++ b/assets/data/excel/chips.xlsx
@@ -1267,7 +1267,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>["CSK007", "CSK008"]</t>
+          <t>["CSK006", "CSK007", "CSK008"]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>["CSK029", "CSK030", "CSK031"]</t>
+          <t>["CSK029", "CSK030", "CSK031", "CSK032"]</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
